--- a/business_surveys/030_facility_cleaning_service_benchmark_survey--business_surveys.xlsx
+++ b/business_surveys/030_facility_cleaning_service_benchmark_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -861,8 +861,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -890,12 +890,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_4,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 4, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_5,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 5, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'office-building',_'label':_'office_building'}</t>
+          <t>office_building</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'office-building', 'label': 'Office Building'}</t>
+          <t>Office Building</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'school-campus',_'label':_'school-campus'}</t>
+          <t>school-campus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'school-campus', 'label': 'School-Campus'}</t>
+          <t>School-Campus</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'hospital-clinic',_'label':_'hospital-clinic'}</t>
+          <t>hospital-clinic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'hospital-clinic', 'label': 'Hospital-Clinic'}</t>
+          <t>Hospital-Clinic</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'retail-store',_'label':_'retail-store'}</t>
+          <t>retail-store</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'retail-store', 'label': 'Retail-Store'}</t>
+          <t>Retail-Store</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'hotel-resort',_'label':_'hotel-resort'}</t>
+          <t>hotel-resort</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'hotel-resort', 'label': 'Hotel-Resort'}</t>
+          <t>Hotel-Resort</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'government-building',_'label':_'government-building'}</t>
+          <t>government-building</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'government-building', 'label': 'Government-Building'}</t>
+          <t>Government-Building</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'restaurant-cafe',_'label':_'restaurant-cafe'}</t>
+          <t>restaurant-cafe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'restaurant-cafe', 'label': 'Restaurant-Cafe'}</t>
+          <t>Restaurant-Cafe</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
